--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -664,15 +664,19 @@
       <c r="K3" t="n">
         <v>1.54</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>AO Away Win</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -696,6 +700,170 @@
       </c>
       <c r="T3" t="n">
         <v>34.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Canadian Premier League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Forge x Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Forge</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Inter Toronto FC</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>198</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="T4" t="n">
+        <v>39.79</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Argentinian Primera C</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AD Berazategui x CD Cambaceres</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AD Berazategui</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CD Cambaceres</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>242</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>41.52</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -601,20 +581,6 @@
       <c r="P2" t="n">
         <v>150</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="T2" t="n">
-        <v>30.81</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,20 +653,6 @@
       <c r="P3" t="n">
         <v>551</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>200</v>
-      </c>
-      <c r="S3" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="T3" t="n">
-        <v>34.1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -750,15 +702,19 @@
       <c r="K4" t="n">
         <v>1.4</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -768,20 +724,6 @@
       </c>
       <c r="P4" t="n">
         <v>198</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="T4" t="n">
-        <v>39.79</v>
       </c>
     </row>
     <row r="5">
@@ -832,15 +774,19 @@
       <c r="K5" t="n">
         <v>1.32</v>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,20 +796,6 @@
       </c>
       <c r="P5" t="n">
         <v>242</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" t="n">
-        <v>43.48</v>
-      </c>
-      <c r="T5" t="n">
-        <v>41.52</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,26 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Hora_Str</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Risco_Red_R$</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Stake_Sugerida_R$</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Lucro_Green_R$</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -581,6 +601,20 @@
       <c r="P2" t="n">
         <v>150</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="R2" t="n">
+        <v>200</v>
+      </c>
+      <c r="S2" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>30.81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -653,6 +687,20 @@
       <c r="P3" t="n">
         <v>551</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>200</v>
+      </c>
+      <c r="S3" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="T3" t="n">
+        <v>34.1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -725,6 +773,20 @@
       <c r="P4" t="n">
         <v>198</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>200</v>
+      </c>
+      <c r="S4" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="T4" t="n">
+        <v>39.79</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -796,6 +858,20 @@
       </c>
       <c r="P5" t="n">
         <v>242</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>200</v>
+      </c>
+      <c r="S5" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="T5" t="n">
+        <v>41.52</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -872,6 +872,88 @@
       </c>
       <c r="T5" t="n">
         <v>41.52</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Criciuma x America MG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lay Draw (Fav &lt;= 1.40)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>LAY</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>PENDENTE</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>⏳ PENDENTE</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>coletor (KO-10)</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>216</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>200</v>
+      </c>
+      <c r="S6" t="n">
+        <v>40</v>
+      </c>
+      <c r="T6" t="n">
+        <v>38.2</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-12.xlsx
@@ -922,15 +922,19 @@
       <c r="K6" t="n">
         <v>1.31</v>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
